--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6630,0.0671,0.0302,0.2123</t>
-  </si>
-  <si>
-    <t>0.0062,0.0002,0.0003,0.9980</t>
-  </si>
-  <si>
-    <t>0.8774,0.0234,0.0155,0.0477</t>
-  </si>
-  <si>
-    <t>0.0422,0.0104,0.0052,0.9802</t>
-  </si>
-  <si>
-    <t>0.9927,0.0006,0.0002,0.0035</t>
-  </si>
-  <si>
-    <t>0.9980,0.0004,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9872,0.0067,0.0010,0.0012</t>
-  </si>
-  <si>
-    <t>0.9928,0.0013,0.0007,0.0017</t>
-  </si>
-  <si>
-    <t>0.9938,0.0035,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9899,0.0062,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9965,0.0007,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.7659,0.1777,0.0162,0.0285</t>
-  </si>
-  <si>
-    <t>0.4938,0.0538,0.5853,0.0108</t>
-  </si>
-  <si>
-    <t>0.2875,0.0398,0.7484,0.0029</t>
-  </si>
-  <si>
-    <t>0.0653,0.0380,0.8755,0.0161</t>
-  </si>
-  <si>
-    <t>0.8500,0.0579,0.0783,0.0160</t>
-  </si>
-  <si>
-    <t>0.0218,0.9769,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.0146,0.9747,0.0082,0.0019</t>
-  </si>
-  <si>
-    <t>0.5061,0.6019,0.0152,0.0054</t>
-  </si>
-  <si>
-    <t>0.2605,0.8436,0.0020,0.0012</t>
-  </si>
-  <si>
-    <t>0.0309,0.9679,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.7214,0.0067,0.2729,0.0339</t>
-  </si>
-  <si>
-    <t>0.3009,0.1985,0.2467,0.4833</t>
-  </si>
-  <si>
-    <t>0.0404,0.0031,0.9627,0.0071</t>
-  </si>
-  <si>
-    <t>0.5000,0.0092,0.7043,0.0029</t>
-  </si>
-  <si>
-    <t>0.1544,0.0035,0.9158,0.0075</t>
-  </si>
-  <si>
-    <t>0.0978,0.0170,0.8465,0.0476</t>
-  </si>
-  <si>
-    <t>0.0013,0.0019,0.9944,0.0036</t>
-  </si>
-  <si>
-    <t>0.4844,0.6802,0.0097,0.0025</t>
-  </si>
-  <si>
-    <t>0.3196,0.5917,0.0394,0.0706</t>
-  </si>
-  <si>
-    <t>0.0031,0.0191,0.9829,0.0053</t>
-  </si>
-  <si>
-    <t>0.0608,0.2715,0.7395,0.0008</t>
-  </si>
-  <si>
-    <t>0.9110,0.0606,0.0086,0.0094</t>
-  </si>
-  <si>
-    <t>0.7307,0.1016,0.2286,0.0148</t>
-  </si>
-  <si>
-    <t>0.6921,0.4133,0.0110,0.0025</t>
-  </si>
-  <si>
-    <t>0.0595,0.8986,0.1269,0.0152</t>
-  </si>
-  <si>
-    <t>0.0104,0.7415,0.0609,0.1833</t>
-  </si>
-  <si>
-    <t>0.0380,0.0352,0.8497,0.1044</t>
-  </si>
-  <si>
-    <t>0.0258,0.4169,0.8051,0.0141</t>
-  </si>
-  <si>
-    <t>0.0544,0.0340,0.9169,0.0067</t>
-  </si>
-  <si>
-    <t>0.0714,0.0408,0.8929,0.0132</t>
-  </si>
-  <si>
-    <t>0.0214,0.5768,0.6687,0.0015</t>
-  </si>
-  <si>
-    <t>0.0159,0.3231,0.9116,0.0118</t>
-  </si>
-  <si>
-    <t>0.5238,0.2216,0.1575,0.2464</t>
-  </si>
-  <si>
-    <t>0.0045,0.9288,0.0076,0.2136</t>
-  </si>
-  <si>
-    <t>0.0009,0.9814,0.1109,0.0010</t>
-  </si>
-  <si>
-    <t>0.0041,0.9724,0.0182,0.0205</t>
-  </si>
-  <si>
-    <t>0.0026,0.0260,0.9806,0.0065</t>
-  </si>
-  <si>
-    <t>0.0014,0.1843,0.9894,0.0002</t>
-  </si>
-  <si>
-    <t>0.1317,0.0287,0.8380,0.0039</t>
-  </si>
-  <si>
-    <t>0.0557,0.0638,0.8709,0.0063</t>
-  </si>
-  <si>
-    <t>0.0141,0.0156,0.9675,0.0084</t>
-  </si>
-  <si>
-    <t>0.0023,0.0360,0.9798,0.0027</t>
-  </si>
-  <si>
-    <t>0.9780,0.0175,0.0006,0.0014</t>
-  </si>
-  <si>
-    <t>0.9507,0.0162,0.0069,0.0116</t>
-  </si>
-  <si>
-    <t>0.9947,0.0011,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.0070,0.0200,0.9831,0.0083</t>
-  </si>
-  <si>
-    <t>0.9850,0.0018,0.0012,0.0055</t>
-  </si>
-  <si>
-    <t>0.9933,0.0023,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9869,0.0096,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.8190,0.9880,0.0001</t>
-  </si>
-  <si>
-    <t>0.0065,0.2250,0.9696,0.0023</t>
-  </si>
-  <si>
-    <t>0.0243,0.1440,0.8001,0.0847</t>
-  </si>
-  <si>
-    <t>0.0005,0.8925,0.9444,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0039,0.9958,0.0040</t>
-  </si>
-  <si>
-    <t>0.0328,0.9162,0.1121,0.0031</t>
-  </si>
-  <si>
-    <t>0.0048,0.9843,0.0017,0.0036</t>
-  </si>
-  <si>
-    <t>0.8084,0.0053,0.2141,0.0188</t>
-  </si>
-  <si>
-    <t>0.5690,0.2706,0.2542,0.0115</t>
-  </si>
-  <si>
-    <t>0.0011,0.0185,0.9936,0.0008</t>
-  </si>
-  <si>
-    <t>0.0059,0.6368,0.8952,0.0019</t>
-  </si>
-  <si>
-    <t>0.0015,0.9631,0.6416,0.0002</t>
-  </si>
-  <si>
-    <t>0.0024,0.9317,0.8377,0.0009</t>
-  </si>
-  <si>
-    <t>0.0048,0.8369,0.9078,0.0015</t>
-  </si>
-  <si>
-    <t>0.0221,0.0145,0.0061,0.9855</t>
-  </si>
-  <si>
-    <t>0.0026,0.0078,0.0007,0.9980</t>
-  </si>
-  <si>
-    <t>0.0257,0.0010,0.0012,0.9910</t>
-  </si>
-  <si>
-    <t>0.0108,0.0042,0.0308,0.9818</t>
-  </si>
-  <si>
-    <t>0.0195,0.0021,0.0146,0.9802</t>
-  </si>
-  <si>
-    <t>0.0096,0.0082,0.0012,0.9945</t>
-  </si>
-  <si>
-    <t>0.0030,0.9353,0.5330,0.0009</t>
-  </si>
-  <si>
-    <t>0.0015,0.6858,0.9648,0.0002</t>
-  </si>
-  <si>
-    <t>0.0072,0.8686,0.4829,0.0014</t>
-  </si>
-  <si>
-    <t>0.0049,0.1487,0.9697,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.8041,0.9735,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.8922,0.5380,0.0011</t>
-  </si>
-  <si>
-    <t>0.9946,0.0028,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9861,0.0078,0.0027,0.0010</t>
-  </si>
-  <si>
-    <t>0.9782,0.0245,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.9950,0.0009,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9871,0.0043,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9923,0.0039,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9883,0.0027,0.0004,0.0025</t>
-  </si>
-  <si>
-    <t>0.9927,0.0065,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9971,0.0012,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0003,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9941,0.0009,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9903,0.0033,0.0010,0.0014</t>
-  </si>
-  <si>
-    <t>0.9962,0.0011,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9928,0.0044,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9972,0.0002,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.0249,0.0023,0.9599,0.0328</t>
-  </si>
-  <si>
-    <t>0.0936,0.0209,0.8819,0.0036</t>
-  </si>
-  <si>
-    <t>0.3578,0.0258,0.0250,0.6928</t>
-  </si>
-  <si>
-    <t>0.0310,0.0427,0.9400,0.0007</t>
-  </si>
-  <si>
-    <t>0.0302,0.9522,0.0082,0.0016</t>
-  </si>
-  <si>
-    <t>0.0461,0.9580,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.1122,0.8677,0.0004,0.0032</t>
-  </si>
-  <si>
-    <t>0.2295,0.8094,0.0022,0.0050</t>
-  </si>
-  <si>
-    <t>0.0523,0.9494,0.0011,0.0009</t>
-  </si>
-  <si>
-    <t>0.0326,0.9600,0.0012,0.0010</t>
-  </si>
-  <si>
-    <t>0.2735,0.8116,0.0016,0.0019</t>
-  </si>
-  <si>
-    <t>0.7995,0.0856,0.1233,0.0088</t>
-  </si>
-  <si>
-    <t>0.1332,0.0761,0.7783,0.0080</t>
-  </si>
-  <si>
-    <t>0.4539,0.3577,0.1982,0.0382</t>
-  </si>
-  <si>
-    <t>0.7286,0.0331,0.3013,0.0274</t>
-  </si>
-  <si>
-    <t>0.1380,0.3435,0.0518,0.8213</t>
-  </si>
-  <si>
-    <t>0.0080,0.9772,0.0082,0.0046</t>
-  </si>
-  <si>
-    <t>0.0104,0.9536,0.1013,0.0056</t>
-  </si>
-  <si>
-    <t>0.0065,0.9625,0.0077,0.0703</t>
-  </si>
-  <si>
-    <t>0.0013,0.9157,0.7998,0.0012</t>
-  </si>
-  <si>
-    <t>0.0769,0.9349,0.0182,0.0001</t>
-  </si>
-  <si>
-    <t>0.5720,0.5238,0.0147,0.0012</t>
-  </si>
-  <si>
-    <t>0.6963,0.4126,0.0167,0.0014</t>
-  </si>
-  <si>
-    <t>0.9806,0.0209,0.0032,0.0006</t>
-  </si>
-  <si>
-    <t>0.9862,0.0011,0.0004,0.0072</t>
-  </si>
-  <si>
-    <t>0.9868,0.0024,0.0005,0.0040</t>
-  </si>
-  <si>
-    <t>0.9849,0.0020,0.0008,0.0056</t>
-  </si>
-  <si>
-    <t>0.9878,0.0027,0.0009,0.0030</t>
-  </si>
-  <si>
-    <t>0.9927,0.0037,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.9863,0.0029,0.0017,0.0026</t>
-  </si>
-  <si>
-    <t>0.9879,0.0007,0.0004,0.0069</t>
-  </si>
-  <si>
-    <t>0.0023,0.9618,0.2935,0.0005</t>
-  </si>
-  <si>
-    <t>0.0030,0.8685,0.5704,0.0002</t>
-  </si>
-  <si>
-    <t>0.0072,0.1763,0.9608,0.0010</t>
-  </si>
-  <si>
-    <t>0.0765,0.3984,0.4936,0.0051</t>
-  </si>
-  <si>
-    <t>0.8421,0.0421,0.0311,0.0423</t>
-  </si>
-  <si>
-    <t>0.8141,0.0881,0.0788,0.0123</t>
-  </si>
-  <si>
-    <t>0.0936,0.0030,0.9572,0.0052</t>
-  </si>
-  <si>
-    <t>0.5998,0.1846,0.0740,0.1404</t>
-  </si>
-  <si>
-    <t>0.0354,0.0154,0.0034,0.9811</t>
-  </si>
-  <si>
-    <t>0.0012,0.0006,0.0003,0.9993</t>
-  </si>
-  <si>
-    <t>0.0008,0.0046,0.0014,0.9989</t>
-  </si>
-  <si>
-    <t>0.0077,0.0002,0.0096,0.9906</t>
-  </si>
-  <si>
-    <t>0.0038,0.3335,0.9316,0.0080</t>
-  </si>
-  <si>
-    <t>0.9546,0.0207,0.0023,0.0077</t>
-  </si>
-  <si>
-    <t>0.1375,0.8808,0.0021,0.0038</t>
-  </si>
-  <si>
-    <t>0.9827,0.0009,0.0009,0.0114</t>
-  </si>
-  <si>
-    <t>0.8044,0.1870,0.0432,0.0029</t>
-  </si>
-  <si>
-    <t>0.9007,0.0046,0.0162,0.0578</t>
-  </si>
-  <si>
-    <t>0.3941,0.0060,0.0159,0.7320</t>
-  </si>
-  <si>
-    <t>0.9670,0.0149,0.0028,0.0045</t>
-  </si>
-  <si>
-    <t>0.0032,0.0813,0.9659,0.0153</t>
-  </si>
-  <si>
-    <t>0.8517,0.0005,0.0014,0.2533</t>
-  </si>
-  <si>
-    <t>0.9114,0.0009,0.0085,0.0527</t>
-  </si>
-  <si>
-    <t>0.1876,0.7835,0.0393,0.0358</t>
-  </si>
-  <si>
-    <t>0.6217,0.4332,0.0116,0.0132</t>
-  </si>
-  <si>
-    <t>0.9373,0.0366,0.0363,0.0011</t>
-  </si>
-  <si>
-    <t>0.0571,0.7493,0.0023,0.2215</t>
-  </si>
-  <si>
-    <t>0.7247,0.2949,0.0302,0.0143</t>
-  </si>
-  <si>
-    <t>0.8704,0.0786,0.0489,0.0058</t>
-  </si>
-  <si>
-    <t>0.9924,0.0009,0.0002,0.0026</t>
-  </si>
-  <si>
-    <t>0.9898,0.0027,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9909,0.0011,0.0002,0.0025</t>
-  </si>
-  <si>
-    <t>0.9907,0.0006,0.0007,0.0040</t>
-  </si>
-  <si>
-    <t>0.9857,0.0028,0.0010,0.0032</t>
-  </si>
-  <si>
-    <t>0.9916,0.0018,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.9928,0.0016,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.9951,0.0012,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.4164,0.6851,0.0164,0.0052</t>
-  </si>
-  <si>
-    <t>0.7641,0.3813,0.0047,0.0007</t>
-  </si>
-  <si>
-    <t>0.5414,0.5769,0.0138,0.0019</t>
-  </si>
-  <si>
-    <t>0.2439,0.1551,0.6895,0.0074</t>
-  </si>
-  <si>
-    <t>0.9337,0.0925,0.0028,0.0010</t>
-  </si>
-  <si>
-    <t>0.5516,0.5126,0.0376,0.0104</t>
-  </si>
-  <si>
-    <t>0.9682,0.0231,0.0016,0.0027</t>
-  </si>
-  <si>
-    <t>0.9166,0.0914,0.0111,0.0049</t>
-  </si>
-  <si>
-    <t>0.0009,0.0156,0.9967,0.0002</t>
-  </si>
-  <si>
-    <t>0.8964,0.1245,0.0131,0.0013</t>
-  </si>
-  <si>
-    <t>0.0016,0.0028,0.9927,0.0041</t>
-  </si>
-  <si>
-    <t>0.0288,0.3021,0.8635,0.0166</t>
-  </si>
-  <si>
-    <t>0.0385,0.0068,0.9605,0.0041</t>
-  </si>
-  <si>
-    <t>0.0016,0.0408,0.9870,0.0032</t>
-  </si>
-  <si>
-    <t>0.0439,0.2247,0.8591,0.0064</t>
-  </si>
-  <si>
-    <t>0.0367,0.0073,0.9633,0.0036</t>
-  </si>
-  <si>
-    <t>0.0068,0.0054,0.9857,0.0037</t>
-  </si>
-  <si>
-    <t>0.2095,0.0234,0.8367,0.0112</t>
-  </si>
-  <si>
-    <t>0.0992,0.0109,0.9190,0.0052</t>
-  </si>
-  <si>
-    <t>0.5192,0.1992,0.3234,0.0104</t>
-  </si>
-  <si>
-    <t>0.4386,0.3128,0.2847,0.0109</t>
-  </si>
-  <si>
-    <t>0.0771,0.3850,0.6440,0.0045</t>
-  </si>
-  <si>
-    <t>0.3497,0.2695,0.3177,0.0113</t>
-  </si>
-  <si>
-    <t>0.2312,0.6070,0.2048,0.1170</t>
-  </si>
-  <si>
-    <t>0.4007,0.0203,0.6886,0.0191</t>
-  </si>
-  <si>
-    <t>0.7603,0.3280,0.0124,0.0022</t>
-  </si>
-  <si>
-    <t>0.8015,0.2966,0.0072,0.0011</t>
-  </si>
-  <si>
-    <t>0.9527,0.0515,0.0047,0.0012</t>
-  </si>
-  <si>
-    <t>0.9946,0.0015,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9609,0.0455,0.0044,0.0014</t>
-  </si>
-  <si>
-    <t>0.5915,0.0324,0.5162,0.0238</t>
-  </si>
-  <si>
-    <t>0.9227,0.0006,0.0082,0.0512</t>
-  </si>
-  <si>
-    <t>0.2867,0.1204,0.0044,0.5598</t>
-  </si>
-  <si>
-    <t>0.6800,0.0410,0.2318,0.1038</t>
-  </si>
-  <si>
-    <t>0.2182,0.5134,0.0781,0.2836</t>
-  </si>
-  <si>
-    <t>0.0154,0.0036,0.9546,0.0858</t>
-  </si>
-  <si>
-    <t>0.0622,0.2485,0.7730,0.0068</t>
-  </si>
-  <si>
-    <t>0.0032,0.5375,0.9539,0.0017</t>
-  </si>
-  <si>
-    <t>0.2190,0.0502,0.7382,0.0227</t>
-  </si>
-  <si>
-    <t>0.1936,0.0967,0.6992,0.0199</t>
-  </si>
-  <si>
-    <t>0.9937,0.0012,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9916,0.0036,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9826,0.0118,0.0016,0.0010</t>
-  </si>
-  <si>
-    <t>0.9944,0.0030,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9928,0.0049,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9847,0.0132,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9927,0.0007,0.0001,0.0028</t>
-  </si>
-  <si>
-    <t>0.9913,0.0048,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.2826,0.0230,0.8077,0.0080</t>
-  </si>
-  <si>
-    <t>0.1198,0.2630,0.6138,0.0029</t>
-  </si>
-  <si>
-    <t>0.8989,0.0566,0.0544,0.0038</t>
-  </si>
-  <si>
-    <t>0.0008,0.0067,0.9871,0.0169</t>
-  </si>
-  <si>
-    <t>0.0011,0.0165,0.9941,0.0008</t>
-  </si>
-  <si>
-    <t>0.0170,0.2294,0.8445,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.0012,0.9979,0.0009</t>
-  </si>
-  <si>
-    <t>0.1397,0.0589,0.7640,0.0587</t>
-  </si>
-  <si>
-    <t>0.0004,0.0029,0.9963,0.0013</t>
-  </si>
-  <si>
-    <t>0.0065,0.0078,0.9603,0.0419</t>
-  </si>
-  <si>
-    <t>0.1636,0.0633,0.8146,0.0190</t>
-  </si>
-  <si>
-    <t>0.8970,0.0018,0.0491,0.0285</t>
-  </si>
-  <si>
-    <t>0.8894,0.0014,0.1663,0.0042</t>
-  </si>
-  <si>
-    <t>0.7848,0.0054,0.0344,0.1650</t>
-  </si>
-  <si>
-    <t>0.9955,0.0016,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9945,0.0036,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9947,0.0025,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9917,0.0043,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9944,0.0016,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9912,0.0037,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9907,0.0016,0.0001,0.0026</t>
-  </si>
-  <si>
-    <t>0.9815,0.0087,0.0014,0.0023</t>
-  </si>
-  <si>
-    <t>0.0158,0.7691,0.6298,0.0044</t>
-  </si>
-  <si>
-    <t>0.0034,0.2226,0.9654,0.0009</t>
-  </si>
-  <si>
-    <t>0.0030,0.0068,0.9845,0.0067</t>
-  </si>
-  <si>
-    <t>0.1722,0.1245,0.5303,0.0018</t>
-  </si>
-  <si>
-    <t>0.0028,0.0010,0.9850,0.0245</t>
-  </si>
-  <si>
-    <t>0.3606,0.0340,0.5773,0.0972</t>
-  </si>
-  <si>
-    <t>0.1112,0.0297,0.8565,0.0158</t>
-  </si>
-  <si>
-    <t>0.0029,0.0029,0.9668,0.0891</t>
-  </si>
-  <si>
-    <t>0.2807,0.0001,0.0007,0.9256</t>
-  </si>
-  <si>
-    <t>0.0222,0.0460,0.0007,0.9845</t>
-  </si>
-  <si>
-    <t>0.0843,0.0128,0.0217,0.9400</t>
-  </si>
-  <si>
-    <t>0.0163,0.0007,0.0011,0.9935</t>
-  </si>
-  <si>
-    <t>0.0030,0.0001,0.0012,0.9978</t>
-  </si>
-  <si>
-    <t>0.8744,0.0099,0.0149,0.1007</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,0,1,1</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.8120,0.0198,0.0219,0.1366</t>
+  </si>
+  <si>
+    <t>0.0210,0.0004,0.0012,0.9925</t>
+  </si>
+  <si>
+    <t>0.8139,0.0178,0.0006,0.1061</t>
+  </si>
+  <si>
+    <t>0.0562,0.0244,0.0137,0.9643</t>
+  </si>
+  <si>
+    <t>0.9959,0.0016,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9950,0.0017,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9970,0.0013,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9907,0.0030,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.9972,0.0005,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9946,0.0007,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9939,0.0004,0.0000,0.0027</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.8866,0.0320,0.0494,0.0134</t>
+  </si>
+  <si>
+    <t>0.1228,0.1333,0.7844,0.0062</t>
+  </si>
+  <si>
+    <t>0.5293,0.0090,0.6881,0.0038</t>
+  </si>
+  <si>
+    <t>0.3075,0.0341,0.7471,0.0149</t>
+  </si>
+  <si>
+    <t>0.8824,0.0262,0.1238,0.0032</t>
+  </si>
+  <si>
+    <t>0.0162,0.9772,0.0028,0.0018</t>
+  </si>
+  <si>
+    <t>0.0851,0.9287,0.0104,0.0010</t>
+  </si>
+  <si>
+    <t>0.5223,0.5974,0.0202,0.0053</t>
+  </si>
+  <si>
+    <t>0.2528,0.8622,0.0030,0.0003</t>
+  </si>
+  <si>
+    <t>0.0334,0.9654,0.0092,0.0003</t>
+  </si>
+  <si>
+    <t>0.8042,0.0058,0.1379,0.0430</t>
+  </si>
+  <si>
+    <t>0.4833,0.0166,0.5922,0.0143</t>
+  </si>
+  <si>
+    <t>0.0835,0.0058,0.9242,0.0213</t>
+  </si>
+  <si>
+    <t>0.2232,0.1588,0.6023,0.0250</t>
+  </si>
+  <si>
+    <t>0.0326,0.0031,0.9777,0.0016</t>
+  </si>
+  <si>
+    <t>0.0510,0.0045,0.9137,0.0774</t>
+  </si>
+  <si>
+    <t>0.0035,0.0029,0.9834,0.0287</t>
+  </si>
+  <si>
+    <t>0.1792,0.8566,0.0116,0.0067</t>
+  </si>
+  <si>
+    <t>0.5443,0.0365,0.6322,0.0044</t>
+  </si>
+  <si>
+    <t>0.0004,0.0141,0.9938,0.0021</t>
+  </si>
+  <si>
+    <t>0.0209,0.9422,0.0466,0.0012</t>
+  </si>
+  <si>
+    <t>0.8238,0.1113,0.0419,0.0228</t>
+  </si>
+  <si>
+    <t>0.8991,0.0839,0.0183,0.0052</t>
+  </si>
+  <si>
+    <t>0.8273,0.2864,0.0035,0.0006</t>
+  </si>
+  <si>
+    <t>0.1128,0.8515,0.1390,0.0044</t>
+  </si>
+  <si>
+    <t>0.0654,0.4953,0.3670,0.0683</t>
+  </si>
+  <si>
+    <t>0.0022,0.0094,0.9703,0.0565</t>
+  </si>
+  <si>
+    <t>0.0441,0.5682,0.6417,0.0722</t>
+  </si>
+  <si>
+    <t>0.5312,0.0252,0.5295,0.0151</t>
+  </si>
+  <si>
+    <t>0.0050,0.4769,0.9006,0.0020</t>
+  </si>
+  <si>
+    <t>0.0210,0.8849,0.2913,0.0024</t>
+  </si>
+  <si>
+    <t>0.0565,0.0408,0.8793,0.0575</t>
+  </si>
+  <si>
+    <t>0.5328,0.1954,0.0541,0.2776</t>
+  </si>
+  <si>
+    <t>0.0321,0.9211,0.0306,0.0227</t>
+  </si>
+  <si>
+    <t>0.0165,0.9303,0.1736,0.0040</t>
+  </si>
+  <si>
+    <t>0.0027,0.9793,0.0144,0.0113</t>
+  </si>
+  <si>
+    <t>0.0654,0.0575,0.8773,0.0107</t>
+  </si>
+  <si>
+    <t>0.0024,0.4366,0.9739,0.0006</t>
+  </si>
+  <si>
+    <t>0.0812,0.0086,0.9183,0.0148</t>
+  </si>
+  <si>
+    <t>0.1155,0.0603,0.7873,0.0047</t>
+  </si>
+  <si>
+    <t>0.0072,0.0252,0.9637,0.0200</t>
+  </si>
+  <si>
+    <t>0.0042,0.3133,0.9420,0.0002</t>
+  </si>
+  <si>
+    <t>0.8928,0.1308,0.0050,0.0041</t>
+  </si>
+  <si>
+    <t>0.9241,0.0005,0.0003,0.1319</t>
+  </si>
+  <si>
+    <t>0.9655,0.0223,0.0009,0.0030</t>
+  </si>
+  <si>
+    <t>0.0034,0.0437,0.9830,0.0044</t>
+  </si>
+  <si>
+    <t>0.9801,0.0126,0.0039,0.0009</t>
+  </si>
+  <si>
+    <t>0.9959,0.0020,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9884,0.0072,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.9350,0.9754,0.0001</t>
+  </si>
+  <si>
+    <t>0.0119,0.0960,0.9633,0.0046</t>
+  </si>
+  <si>
+    <t>0.0054,0.1184,0.9545,0.0021</t>
+  </si>
+  <si>
+    <t>0.0003,0.9038,0.9658,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.0072,0.9925,0.0035</t>
+  </si>
+  <si>
+    <t>0.1040,0.8832,0.0309,0.0007</t>
+  </si>
+  <si>
+    <t>0.0465,0.9586,0.0040,0.0009</t>
+  </si>
+  <si>
+    <t>0.9460,0.0264,0.0281,0.0024</t>
+  </si>
+  <si>
+    <t>0.5192,0.2591,0.2889,0.0054</t>
+  </si>
+  <si>
+    <t>0.0009,0.1968,0.9894,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.9176,0.8707,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.9706,0.5240,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.9802,0.2028,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.9040,0.8410,0.0008</t>
+  </si>
+  <si>
+    <t>0.1401,0.0009,0.0058,0.9410</t>
+  </si>
+  <si>
+    <t>0.0009,0.0007,0.0006,0.9993</t>
+  </si>
+  <si>
+    <t>0.0104,0.0045,0.0014,0.9945</t>
+  </si>
+  <si>
+    <t>0.0086,0.0004,0.0086,0.9914</t>
+  </si>
+  <si>
+    <t>0.0166,0.0027,0.0020,0.9926</t>
+  </si>
+  <si>
+    <t>0.0035,0.0063,0.0007,0.9975</t>
+  </si>
+  <si>
+    <t>0.0027,0.8456,0.9203,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.8353,0.9739,0.0001</t>
+  </si>
+  <si>
+    <t>0.0136,0.8469,0.4043,0.0080</t>
+  </si>
+  <si>
+    <t>0.0012,0.8380,0.8966,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.9211,0.8314,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.8654,0.6070,0.0010</t>
+  </si>
+  <si>
+    <t>0.9768,0.0095,0.0079,0.0025</t>
+  </si>
+  <si>
+    <t>0.9836,0.0093,0.0017,0.0011</t>
+  </si>
+  <si>
+    <t>0.9932,0.0075,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9921,0.0026,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9877,0.0065,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.9966,0.0004,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9928,0.0042,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9890,0.0053,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.9956,0.0006,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9945,0.0027,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9966,0.0002,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9955,0.0036,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9952,0.0021,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9971,0.0002,0.0000,0.0009</t>
+  </si>
+  <si>
+    <t>0.0112,0.0051,0.9879,0.0016</t>
+  </si>
+  <si>
+    <t>0.1447,0.0230,0.8396,0.0368</t>
+  </si>
+  <si>
+    <t>0.0650,0.3389,0.0017,0.7488</t>
+  </si>
+  <si>
+    <t>0.0169,0.0059,0.9690,0.0096</t>
+  </si>
+  <si>
+    <t>0.0801,0.9328,0.0108,0.0005</t>
+  </si>
+  <si>
+    <t>0.0995,0.9206,0.0074,0.0005</t>
+  </si>
+  <si>
+    <t>0.0229,0.9592,0.0004,0.0019</t>
+  </si>
+  <si>
+    <t>0.1403,0.8735,0.0032,0.0040</t>
+  </si>
+  <si>
+    <t>0.0990,0.9164,0.0059,0.0019</t>
+  </si>
+  <si>
+    <t>0.0569,0.9503,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.3220,0.8177,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.7957,0.0536,0.1434,0.0376</t>
+  </si>
+  <si>
+    <t>0.3140,0.0233,0.7499,0.0075</t>
+  </si>
+  <si>
+    <t>0.4987,0.2675,0.2642,0.0605</t>
+  </si>
+  <si>
+    <t>0.5260,0.0890,0.4515,0.0098</t>
+  </si>
+  <si>
+    <t>0.1408,0.0440,0.0981,0.8035</t>
+  </si>
+  <si>
+    <t>0.0030,0.9876,0.0198,0.0005</t>
+  </si>
+  <si>
+    <t>0.0120,0.9659,0.0093,0.0068</t>
+  </si>
+  <si>
+    <t>0.0215,0.9390,0.0128,0.0276</t>
+  </si>
+  <si>
+    <t>0.0025,0.7292,0.9563,0.0015</t>
+  </si>
+  <si>
+    <t>0.1116,0.9185,0.0153,0.0001</t>
+  </si>
+  <si>
+    <t>0.6042,0.4756,0.0193,0.0010</t>
+  </si>
+  <si>
+    <t>0.1988,0.8461,0.0096,0.0032</t>
+  </si>
+  <si>
+    <t>0.9950,0.0021,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9797,0.0051,0.0007,0.0055</t>
+  </si>
+  <si>
+    <t>0.9948,0.0003,0.0001,0.0024</t>
+  </si>
+  <si>
+    <t>0.9678,0.0029,0.0046,0.0140</t>
+  </si>
+  <si>
+    <t>0.9892,0.0084,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9845,0.0054,0.0064,0.0017</t>
+  </si>
+  <si>
+    <t>0.9905,0.0020,0.0007,0.0020</t>
+  </si>
+  <si>
+    <t>0.9922,0.0009,0.0007,0.0020</t>
+  </si>
+  <si>
+    <t>0.0073,0.7136,0.8941,0.0055</t>
+  </si>
+  <si>
+    <t>0.0010,0.9305,0.8742,0.0002</t>
+  </si>
+  <si>
+    <t>0.0112,0.1057,0.9397,0.0025</t>
+  </si>
+  <si>
+    <t>0.0178,0.0840,0.9424,0.0021</t>
+  </si>
+  <si>
+    <t>0.8798,0.0229,0.0614,0.0220</t>
+  </si>
+  <si>
+    <t>0.5970,0.0606,0.4328,0.0364</t>
+  </si>
+  <si>
+    <t>0.1679,0.0036,0.8150,0.0617</t>
+  </si>
+  <si>
+    <t>0.5822,0.2005,0.2600,0.0423</t>
+  </si>
+  <si>
+    <t>0.0326,0.0023,0.0050,0.9819</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0010,0.9998</t>
+  </si>
+  <si>
+    <t>0.0030,0.0088,0.0016,0.9972</t>
+  </si>
+  <si>
+    <t>0.0047,0.0001,0.0007,0.9980</t>
+  </si>
+  <si>
+    <t>0.0057,0.6442,0.9140,0.0034</t>
+  </si>
+  <si>
+    <t>0.9636,0.0281,0.0019,0.0025</t>
+  </si>
+  <si>
+    <t>0.4520,0.5199,0.0046,0.0312</t>
+  </si>
+  <si>
+    <t>0.9889,0.0030,0.0008,0.0017</t>
+  </si>
+  <si>
+    <t>0.8946,0.1290,0.0105,0.0023</t>
+  </si>
+  <si>
+    <t>0.9726,0.0017,0.0012,0.0192</t>
+  </si>
+  <si>
+    <t>0.4255,0.0057,0.0395,0.6182</t>
+  </si>
+  <si>
+    <t>0.9458,0.0164,0.0043,0.0153</t>
+  </si>
+  <si>
+    <t>0.0029,0.1553,0.9525,0.0229</t>
+  </si>
+  <si>
+    <t>0.8089,0.0005,0.0100,0.1838</t>
+  </si>
+  <si>
+    <t>0.8850,0.0027,0.0167,0.0611</t>
+  </si>
+  <si>
+    <t>0.4910,0.6380,0.0071,0.0038</t>
+  </si>
+  <si>
+    <t>0.1441,0.8325,0.0034,0.0214</t>
+  </si>
+  <si>
+    <t>0.9269,0.0634,0.0159,0.0025</t>
+  </si>
+  <si>
+    <t>0.5216,0.2043,0.3829,0.0524</t>
+  </si>
+  <si>
+    <t>0.6661,0.2792,0.1292,0.0301</t>
+  </si>
+  <si>
+    <t>0.7837,0.2020,0.0480,0.0053</t>
+  </si>
+  <si>
+    <t>0.9873,0.0006,0.0002,0.0084</t>
+  </si>
+  <si>
+    <t>0.9938,0.0014,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9935,0.0037,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9892,0.0003,0.0003,0.0104</t>
+  </si>
+  <si>
+    <t>0.9785,0.0055,0.0006,0.0049</t>
+  </si>
+  <si>
+    <t>0.9876,0.0012,0.0007,0.0048</t>
+  </si>
+  <si>
+    <t>0.9966,0.0002,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9843,0.0018,0.0003,0.0072</t>
+  </si>
+  <si>
+    <t>0.4278,0.7035,0.0126,0.0037</t>
+  </si>
+  <si>
+    <t>0.6559,0.4438,0.0208,0.0009</t>
+  </si>
+  <si>
+    <t>0.5839,0.5921,0.0065,0.0026</t>
+  </si>
+  <si>
+    <t>0.5843,0.1135,0.3708,0.0049</t>
+  </si>
+  <si>
+    <t>0.9416,0.0443,0.0005,0.0032</t>
+  </si>
+  <si>
+    <t>0.9021,0.0659,0.0052,0.0141</t>
+  </si>
+  <si>
+    <t>0.9853,0.0041,0.0008,0.0024</t>
+  </si>
+  <si>
+    <t>0.4967,0.2100,0.0003,0.0338</t>
+  </si>
+  <si>
+    <t>0.0004,0.0062,0.9975,0.0009</t>
+  </si>
+  <si>
+    <t>0.8985,0.1344,0.0053,0.0016</t>
+  </si>
+  <si>
+    <t>0.0046,0.0049,0.9865,0.0038</t>
+  </si>
+  <si>
+    <t>0.0097,0.4788,0.8284,0.0188</t>
+  </si>
+  <si>
+    <t>0.0153,0.0032,0.9831,0.0030</t>
+  </si>
+  <si>
+    <t>0.0211,0.0468,0.9497,0.0071</t>
+  </si>
+  <si>
+    <t>0.0104,0.1740,0.9355,0.0022</t>
+  </si>
+  <si>
+    <t>0.0532,0.0092,0.9523,0.0060</t>
+  </si>
+  <si>
+    <t>0.0129,0.0025,0.9843,0.0042</t>
+  </si>
+  <si>
+    <t>0.0948,0.0492,0.8404,0.0120</t>
+  </si>
+  <si>
+    <t>0.0724,0.0203,0.8993,0.0018</t>
+  </si>
+  <si>
+    <t>0.2471,0.1168,0.6478,0.0201</t>
+  </si>
+  <si>
+    <t>0.5900,0.0546,0.4717,0.0189</t>
+  </si>
+  <si>
+    <t>0.4282,0.3105,0.3057,0.0072</t>
+  </si>
+  <si>
+    <t>0.3179,0.0842,0.6277,0.0245</t>
+  </si>
+  <si>
+    <t>0.8104,0.0337,0.1663,0.0168</t>
+  </si>
+  <si>
+    <t>0.1546,0.0195,0.8855,0.0052</t>
+  </si>
+  <si>
+    <t>0.8924,0.1785,0.0017,0.0012</t>
+  </si>
+  <si>
+    <t>0.8397,0.2238,0.0088,0.0008</t>
+  </si>
+  <si>
+    <t>0.9524,0.0342,0.0175,0.0023</t>
+  </si>
+  <si>
+    <t>0.9680,0.0325,0.0033,0.0014</t>
+  </si>
+  <si>
+    <t>0.6489,0.4851,0.0069,0.0028</t>
+  </si>
+  <si>
+    <t>0.7325,0.0448,0.2508,0.0215</t>
+  </si>
+  <si>
+    <t>0.7236,0.0296,0.3882,0.0060</t>
+  </si>
+  <si>
+    <t>0.7846,0.0315,0.0609,0.0806</t>
+  </si>
+  <si>
+    <t>0.5323,0.0988,0.3584,0.0567</t>
+  </si>
+  <si>
+    <t>0.6196,0.0095,0.4248,0.0282</t>
+  </si>
+  <si>
+    <t>0.0177,0.0151,0.9630,0.0120</t>
+  </si>
+  <si>
+    <t>0.0098,0.6340,0.7280,0.0606</t>
+  </si>
+  <si>
+    <t>0.0188,0.3140,0.8892,0.0049</t>
+  </si>
+  <si>
+    <t>0.0940,0.0435,0.8365,0.0465</t>
+  </si>
+  <si>
+    <t>0.0166,0.3806,0.8102,0.0045</t>
+  </si>
+  <si>
+    <t>0.9954,0.0037,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9853,0.0131,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9878,0.0071,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9722,0.0280,0.0045,0.0010</t>
+  </si>
+  <si>
+    <t>0.9891,0.0081,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9930,0.0032,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9947,0.0008,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9794,0.0184,0.0021,0.0014</t>
+  </si>
+  <si>
+    <t>0.1439,0.0286,0.8746,0.0090</t>
+  </si>
+  <si>
+    <t>0.0420,0.6492,0.5732,0.0113</t>
+  </si>
+  <si>
+    <t>0.9200,0.0525,0.0245,0.0064</t>
+  </si>
+  <si>
+    <t>0.0295,0.2222,0.8034,0.0035</t>
+  </si>
+  <si>
+    <t>0.0007,0.0524,0.9868,0.0040</t>
+  </si>
+  <si>
+    <t>0.0746,0.0285,0.9151,0.0008</t>
+  </si>
+  <si>
+    <t>0.0016,0.0062,0.9945,0.0006</t>
+  </si>
+  <si>
+    <t>0.0278,0.5054,0.5684,0.0114</t>
+  </si>
+  <si>
+    <t>0.0014,0.0114,0.9881,0.0080</t>
+  </si>
+  <si>
+    <t>0.0060,0.0466,0.9700,0.0046</t>
+  </si>
+  <si>
+    <t>0.2891,0.0546,0.7145,0.0620</t>
+  </si>
+  <si>
+    <t>0.6996,0.0304,0.2965,0.0417</t>
+  </si>
+  <si>
+    <t>0.6696,0.0051,0.4535,0.0134</t>
+  </si>
+  <si>
+    <t>0.7598,0.0291,0.0581,0.1000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0007,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9926,0.0021,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9969,0.0009,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9867,0.0125,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9474,0.0387,0.0062,0.0078</t>
+  </si>
+  <si>
+    <t>0.9947,0.0013,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9908,0.0012,0.0002,0.0025</t>
+  </si>
+  <si>
+    <t>0.9821,0.0061,0.0008,0.0030</t>
+  </si>
+  <si>
+    <t>0.0929,0.0935,0.8348,0.0056</t>
+  </si>
+  <si>
+    <t>0.0043,0.2954,0.9648,0.0011</t>
+  </si>
+  <si>
+    <t>0.0078,0.0299,0.9748,0.0061</t>
+  </si>
+  <si>
+    <t>0.0754,0.3389,0.4770,0.0060</t>
+  </si>
+  <si>
+    <t>0.0070,0.0101,0.9833,0.0044</t>
+  </si>
+  <si>
+    <t>0.0477,0.0227,0.6613,0.5104</t>
+  </si>
+  <si>
+    <t>0.3236,0.0276,0.7200,0.0199</t>
+  </si>
+  <si>
+    <t>0.0374,0.0156,0.9275,0.0169</t>
+  </si>
+  <si>
+    <t>0.6336,0.0011,0.0025,0.5615</t>
+  </si>
+  <si>
+    <t>0.0205,0.0078,0.0041,0.9873</t>
+  </si>
+  <si>
+    <t>0.0063,0.0118,0.0018,0.9954</t>
+  </si>
+  <si>
+    <t>0.0018,0.0005,0.0011,0.9985</t>
+  </si>
+  <si>
+    <t>0.0006,0.0010,0.0020,0.9988</t>
+  </si>
+  <si>
+    <t>0.6149,0.0500,0.2070,0.2053</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2013,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2139,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2153,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2164,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2195,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2234,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2279,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2290,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2377,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2388,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2416,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2447,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2461,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2486,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2514,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2528,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2545,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,10 +2556,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2587,7 @@
         <v>259</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2657,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2755,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2825,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2867,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2923,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2937,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2965,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2979,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2990,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3007,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3105,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3119,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3133,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3144,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3161,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3175,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3441,7 @@
         <v>260</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3553,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3567,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3581,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3592,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3609,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3623,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3679,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3704,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3718,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3844,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3861,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3875,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3886,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3931,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3959,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4012,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4043,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4071,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4099,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4127,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4169,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,10 +4180,10 @@
         <v>259</v>
       </c>
       <c r="C160" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4208,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4365,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4379,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4390,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4404,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4421,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,10 +4432,10 @@
         <v>259</v>
       </c>
       <c r="C178" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,10 +4460,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4603,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4617,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4628,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4645,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4656,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4670,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4684,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4701,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4715,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4729,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4743,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4771,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4782,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4810,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4827,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4838,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4866,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4880,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4897,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4911,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5048,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5107,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5132,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5342,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5384,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5412,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5429,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5454,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5485,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5527,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
